--- a/GBDS JULY FILES 2026/PIRM 2025 Q3.xlsx
+++ b/GBDS JULY FILES 2026/PIRM 2025 Q3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9ed2057538f5012f/Desktop/Guillermo 2025/Giullermo Promo 2025/Guillermo Promo 2025-3Q/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS JULY FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{4BDD4FC9-2182-4DFC-9BB7-47E5014F122A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8028817E-FCEB-4603-A3C0-51C692F2E39D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB5D387-8D96-4132-96D4-21116D50BE8A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{90A4BF69-F41C-4D57-82A3-8979CB5194E7}"/>
+    <workbookView xWindow="-120" yWindow="480" windowWidth="29040" windowHeight="15840" xr2:uid="{90A4BF69-F41C-4D57-82A3-8979CB5194E7}"/>
   </bookViews>
   <sheets>
     <sheet name="PIRM 2025 Q3" sheetId="2" r:id="rId1"/>
@@ -26,12 +26,7 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -502,8 +497,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
@@ -780,7 +775,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -802,19 +797,19 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -829,7 +824,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -841,10 +836,10 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -865,19 +860,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -895,16 +890,16 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -925,7 +920,10 @@
     <xf numFmtId="49" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="5" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -945,9 +943,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -973,9 +968,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1013,7 +1008,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1119,7 +1114,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1261,7 +1256,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1270,26 +1265,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA0D39C-03DD-4F5F-A8A3-9EE6F2CE0166}">
   <dimension ref="A1:M142"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="18" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="36.109375" style="3" customWidth="1"/>
-    <col min="3" max="4" width="17.44140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="21.6640625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="3"/>
-    <col min="7" max="8" width="17.5546875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="15.85546875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" style="3" customWidth="1"/>
+    <col min="3" max="4" width="17.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" style="3" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="3"/>
+    <col min="7" max="8" width="17.5703125" style="3" customWidth="1"/>
     <col min="9" max="9" width="31" style="3" customWidth="1"/>
     <col min="10" max="10" width="20" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="17.5546875" style="3" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="3"/>
+    <col min="11" max="13" width="17.5703125" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1300,71 +1295,71 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="C4" s="7">
         <f>SUM(C9:C142)</f>
         <v>391395.5</v>
       </c>
       <c r="D4" s="7">
-        <f>SUM(D7:D87)</f>
-        <v>107787</v>
+        <f>SUM(D7:D98)</f>
+        <v>314487</v>
       </c>
       <c r="E4" s="8">
         <f>D4-C4</f>
-        <v>-283608.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="51" t="s">
+        <v>-76908.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="54"/>
-      <c r="E5" s="49" t="s">
+      <c r="D5" s="55"/>
+      <c r="E5" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="49" t="s">
+      <c r="G5" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="H5" s="49" t="s">
+      <c r="H5" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="I5" s="49" t="s">
+      <c r="I5" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="49" t="s">
+      <c r="J5" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="K5" s="49" t="s">
+      <c r="K5" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="L5" s="49" t="s">
+      <c r="L5" s="50" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="52"/>
-      <c r="B6" s="50"/>
+    <row r="6" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="53"/>
+      <c r="B6" s="51"/>
       <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
-      <c r="J6" s="50"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-    </row>
-    <row r="7" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="E6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
+      <c r="I6" s="51"/>
+      <c r="J6" s="51"/>
+      <c r="K6" s="51"/>
+      <c r="L6" s="51"/>
+    </row>
+    <row r="7" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="25"/>
       <c r="B7" s="26" t="s">
         <v>140</v>
@@ -1381,7 +1376,7 @@
       <c r="K7" s="24"/>
       <c r="L7" s="24"/>
     </row>
-    <row r="8" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>23</v>
       </c>
@@ -1396,7 +1391,7 @@
       <c r="K8" s="12"/>
       <c r="L8" s="12"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="18">
         <v>45839</v>
       </c>
@@ -1424,7 +1419,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="18">
         <v>45840</v>
       </c>
@@ -1452,7 +1447,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="18">
         <v>45840</v>
       </c>
@@ -1480,7 +1475,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="18">
         <v>45840</v>
       </c>
@@ -1508,7 +1503,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="18">
         <v>45840</v>
       </c>
@@ -1536,7 +1531,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="18">
         <v>45840</v>
       </c>
@@ -1564,7 +1559,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="18">
         <v>45840</v>
       </c>
@@ -1592,7 +1587,7 @@
         <v>3615</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
         <v>45840</v>
       </c>
@@ -1620,7 +1615,7 @@
         <v>3616</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="18">
         <v>45840</v>
       </c>
@@ -1648,7 +1643,7 @@
         <v>3618</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="18">
         <v>45840</v>
       </c>
@@ -1676,7 +1671,7 @@
         <v>3619</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="18">
         <v>45840</v>
       </c>
@@ -1704,7 +1699,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="18">
         <v>45840</v>
       </c>
@@ -1732,7 +1727,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="18">
         <v>45840</v>
       </c>
@@ -1760,7 +1755,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="18">
         <v>45846</v>
       </c>
@@ -1788,7 +1783,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="18">
         <v>45850</v>
       </c>
@@ -1816,7 +1811,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="18">
         <v>45850</v>
       </c>
@@ -1844,7 +1839,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="18">
         <v>45850</v>
       </c>
@@ -1872,7 +1867,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="18">
         <v>45850</v>
       </c>
@@ -1900,7 +1895,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="18">
         <v>45850</v>
       </c>
@@ -1928,7 +1923,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="18">
         <v>45850</v>
       </c>
@@ -1956,7 +1951,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18">
         <v>45864</v>
       </c>
@@ -1984,7 +1979,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="18">
         <v>45867</v>
       </c>
@@ -2013,7 +2008,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="18">
         <v>45868</v>
       </c>
@@ -2042,7 +2037,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="18">
         <v>45869</v>
       </c>
@@ -2071,7 +2066,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="18">
         <v>45869</v>
       </c>
@@ -2100,7 +2095,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="18"/>
       <c r="B34" s="19"/>
       <c r="C34" s="20"/>
@@ -2114,7 +2109,7 @@
       <c r="K34" s="19"/>
       <c r="L34" s="23"/>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="44" t="s">
         <v>21</v>
       </c>
@@ -2130,7 +2125,7 @@
       <c r="K35" s="19"/>
       <c r="L35" s="23"/>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="18">
         <v>45839</v>
       </c>
@@ -2158,7 +2153,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="18">
         <v>45839</v>
       </c>
@@ -2186,7 +2181,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="18">
         <v>45839</v>
       </c>
@@ -2214,7 +2209,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="18">
         <v>45839</v>
       </c>
@@ -2242,7 +2237,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="18">
         <v>45839</v>
       </c>
@@ -2270,7 +2265,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="18">
         <v>45841</v>
       </c>
@@ -2299,7 +2294,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="18">
         <v>45841</v>
       </c>
@@ -2328,7 +2323,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" s="18">
         <v>45842</v>
       </c>
@@ -2357,7 +2352,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" s="18">
         <v>45842</v>
       </c>
@@ -2385,7 +2380,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="18">
         <v>45843</v>
       </c>
@@ -2414,7 +2409,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="18">
         <v>45845</v>
       </c>
@@ -2443,7 +2438,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="18">
         <v>45846</v>
       </c>
@@ -2472,7 +2467,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="18">
         <v>45850</v>
       </c>
@@ -2501,7 +2496,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="18">
         <v>45861</v>
       </c>
@@ -2530,7 +2525,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="18">
         <v>45866</v>
       </c>
@@ -2559,7 +2554,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="18">
         <v>45867</v>
       </c>
@@ -2588,7 +2583,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="18">
         <v>45867</v>
       </c>
@@ -2617,7 +2612,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="18">
         <v>45868</v>
       </c>
@@ -2646,7 +2641,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="18">
         <v>45868</v>
       </c>
@@ -2675,7 +2670,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="18">
         <v>45868</v>
       </c>
@@ -2704,7 +2699,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="18">
         <v>45869</v>
       </c>
@@ -2733,7 +2728,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="18"/>
       <c r="B57" s="19"/>
       <c r="C57" s="20"/>
@@ -2747,7 +2742,7 @@
       <c r="K57" s="19"/>
       <c r="L57" s="23"/>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="45" t="s">
         <v>22</v>
       </c>
@@ -2763,7 +2758,7 @@
       <c r="K58" s="19"/>
       <c r="L58" s="23"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="18">
         <v>45839</v>
       </c>
@@ -2792,7 +2787,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="60" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:12" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="18">
         <v>45839</v>
       </c>
@@ -2820,7 +2815,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="18">
         <v>45840</v>
       </c>
@@ -2848,7 +2843,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="18">
         <v>45841</v>
       </c>
@@ -2876,7 +2871,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="18">
         <v>45841</v>
       </c>
@@ -2902,7 +2897,7 @@
       <c r="K63" s="19"/>
       <c r="L63" s="23"/>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="18">
         <v>45841</v>
       </c>
@@ -2928,7 +2923,7 @@
       <c r="K64" s="19"/>
       <c r="L64" s="23"/>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A65" s="18">
         <v>45841</v>
       </c>
@@ -2956,7 +2951,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A66" s="18">
         <v>45842</v>
       </c>
@@ -2985,7 +2980,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A67" s="18">
         <v>45863</v>
       </c>
@@ -3014,7 +3009,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A68" s="18">
         <v>45866</v>
       </c>
@@ -3043,7 +3038,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A69" s="18">
         <v>45867</v>
       </c>
@@ -3072,7 +3067,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A70" s="18">
         <v>45867</v>
       </c>
@@ -3101,7 +3096,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="18">
         <v>45867</v>
       </c>
@@ -3133,7 +3128,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A72" s="18">
         <v>45868</v>
       </c>
@@ -3162,7 +3157,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="73" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="18">
         <v>45868</v>
       </c>
@@ -3194,7 +3189,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="74" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="18">
         <v>45868</v>
       </c>
@@ -3222,7 +3217,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="75" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="18">
         <v>45869</v>
       </c>
@@ -3250,7 +3245,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="76" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="18">
         <v>45869</v>
       </c>
@@ -3281,7 +3276,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="77" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="18">
         <v>45869</v>
       </c>
@@ -3309,7 +3304,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="78" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="18">
         <v>45869</v>
       </c>
@@ -3337,7 +3332,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="79" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="18">
         <v>45869</v>
       </c>
@@ -3368,7 +3363,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="80" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="18">
         <v>45869</v>
       </c>
@@ -3396,7 +3391,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="81" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="18">
         <v>45869</v>
       </c>
@@ -3427,7 +3422,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="18"/>
       <c r="B82" s="19"/>
       <c r="C82" s="20"/>
@@ -3441,7 +3436,7 @@
       <c r="K82" s="19"/>
       <c r="L82" s="23"/>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="45" t="s">
         <v>23</v>
       </c>
@@ -3457,7 +3452,7 @@
       <c r="K83" s="19"/>
       <c r="L83" s="23"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="45"/>
       <c r="B84" s="19"/>
       <c r="C84" s="20"/>
@@ -3471,7 +3466,7 @@
       <c r="K84" s="19"/>
       <c r="L84" s="23"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="45" t="s">
         <v>21</v>
       </c>
@@ -3487,7 +3482,7 @@
       <c r="K85" s="19"/>
       <c r="L85" s="23"/>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="18">
         <v>45871</v>
       </c>
@@ -3516,7 +3511,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="18">
         <v>45871</v>
       </c>
@@ -3545,7 +3540,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A88" s="45" t="s">
         <v>22</v>
       </c>
@@ -3561,7 +3556,7 @@
       <c r="K88" s="19"/>
       <c r="L88" s="23"/>
     </row>
-    <row r="89" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:13" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="18">
         <v>45870</v>
       </c>
@@ -3580,7 +3575,7 @@
       <c r="H89" s="19">
         <v>3</v>
       </c>
-      <c r="I89" s="55" t="s">
+      <c r="I89" s="49" t="s">
         <v>144</v>
       </c>
       <c r="J89" s="19" t="s">
@@ -3594,7 +3589,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="18">
         <v>45882</v>
       </c>
@@ -3621,7 +3616,7 @@
       <c r="K90" s="19"/>
       <c r="L90" s="23"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="18">
         <v>45882</v>
       </c>
@@ -3647,7 +3642,7 @@
       <c r="K91" s="19"/>
       <c r="L91" s="23"/>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A92" s="18">
         <v>45882</v>
       </c>
@@ -3673,11 +3668,14 @@
       <c r="K92" s="19"/>
       <c r="L92" s="23"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="18"/>
       <c r="B93" s="19"/>
       <c r="C93" s="20"/>
-      <c r="D93" s="21"/>
+      <c r="D93" s="21">
+        <f>650*318</f>
+        <v>206700</v>
+      </c>
       <c r="E93" s="19"/>
       <c r="F93" s="22"/>
       <c r="G93" s="19"/>
@@ -3687,7 +3685,7 @@
       <c r="K93" s="19"/>
       <c r="L93" s="23"/>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A94" s="18"/>
       <c r="B94" s="19"/>
       <c r="C94" s="20"/>
@@ -3701,7 +3699,7 @@
       <c r="K94" s="19"/>
       <c r="L94" s="23"/>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A95" s="18"/>
       <c r="B95" s="19"/>
       <c r="C95" s="20"/>
@@ -3715,7 +3713,7 @@
       <c r="K95" s="19"/>
       <c r="L95" s="23"/>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A96" s="18"/>
       <c r="B96" s="19"/>
       <c r="C96" s="20"/>
@@ -3729,7 +3727,7 @@
       <c r="K96" s="19"/>
       <c r="L96" s="23"/>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" s="18"/>
       <c r="B97" s="19"/>
       <c r="C97" s="20"/>
@@ -3743,7 +3741,7 @@
       <c r="K97" s="19"/>
       <c r="L97" s="23"/>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" s="18"/>
       <c r="B98" s="19"/>
       <c r="C98" s="20"/>
@@ -3757,7 +3755,7 @@
       <c r="K98" s="19"/>
       <c r="L98" s="23"/>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="18"/>
       <c r="B99" s="19"/>
       <c r="C99" s="20"/>
@@ -3771,7 +3769,7 @@
       <c r="K99" s="19"/>
       <c r="L99" s="23"/>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" s="18"/>
       <c r="B100" s="19"/>
       <c r="C100" s="20"/>
@@ -3785,7 +3783,7 @@
       <c r="K100" s="19"/>
       <c r="L100" s="23"/>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" s="18"/>
       <c r="B101" s="19"/>
       <c r="C101" s="20"/>
@@ -3799,7 +3797,7 @@
       <c r="K101" s="19"/>
       <c r="L101" s="23"/>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" s="18"/>
       <c r="B102" s="19"/>
       <c r="C102" s="20"/>
@@ -3813,7 +3811,7 @@
       <c r="K102" s="19"/>
       <c r="L102" s="23"/>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" s="18"/>
       <c r="B103" s="19"/>
       <c r="C103" s="20"/>
@@ -3827,7 +3825,7 @@
       <c r="K103" s="19"/>
       <c r="L103" s="23"/>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="6"/>
       <c r="C104" s="16"/>
@@ -3840,7 +3838,7 @@
       <c r="K104" s="6"/>
       <c r="L104" s="10"/>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="6"/>
       <c r="C105" s="16"/>
@@ -3853,7 +3851,7 @@
       <c r="K105" s="6"/>
       <c r="L105" s="10"/>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="6"/>
       <c r="C106" s="16"/>
@@ -3866,7 +3864,7 @@
       <c r="K106" s="6"/>
       <c r="L106" s="10"/>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="6"/>
       <c r="C107" s="16"/>
@@ -3879,7 +3877,7 @@
       <c r="K107" s="6"/>
       <c r="L107" s="10"/>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="6"/>
       <c r="C108" s="16"/>
@@ -3892,7 +3890,7 @@
       <c r="K108" s="6"/>
       <c r="L108" s="10"/>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="6"/>
       <c r="C109" s="16"/>
@@ -3905,7 +3903,7 @@
       <c r="K109" s="6"/>
       <c r="L109" s="10"/>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="6"/>
       <c r="C110" s="16"/>
@@ -3918,7 +3916,7 @@
       <c r="K110" s="6"/>
       <c r="L110" s="10"/>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="6"/>
       <c r="C111" s="16"/>
@@ -3931,7 +3929,7 @@
       <c r="K111" s="6"/>
       <c r="L111" s="10"/>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="6"/>
       <c r="C112" s="16"/>
@@ -3944,7 +3942,7 @@
       <c r="K112" s="6"/>
       <c r="L112" s="10"/>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="6"/>
       <c r="C113" s="16"/>
@@ -3957,7 +3955,7 @@
       <c r="K113" s="6"/>
       <c r="L113" s="10"/>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="6"/>
       <c r="C114" s="16"/>
@@ -3970,7 +3968,7 @@
       <c r="K114" s="6"/>
       <c r="L114" s="10"/>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="6"/>
       <c r="C115" s="16"/>
@@ -3983,7 +3981,7 @@
       <c r="K115" s="6"/>
       <c r="L115" s="10"/>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="6"/>
       <c r="C116" s="16"/>
@@ -3996,7 +3994,7 @@
       <c r="K116" s="6"/>
       <c r="L116" s="10"/>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="6"/>
       <c r="C117" s="16"/>
@@ -4009,7 +4007,7 @@
       <c r="K117" s="6"/>
       <c r="L117" s="10"/>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="6"/>
       <c r="C118" s="16"/>
@@ -4022,7 +4020,7 @@
       <c r="K118" s="6"/>
       <c r="L118" s="10"/>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="6"/>
       <c r="C119" s="16"/>
@@ -4035,7 +4033,7 @@
       <c r="K119" s="6"/>
       <c r="L119" s="10"/>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="6"/>
       <c r="C120" s="16"/>
@@ -4048,7 +4046,7 @@
       <c r="K120" s="6"/>
       <c r="L120" s="10"/>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="6"/>
       <c r="C121" s="16"/>
@@ -4061,7 +4059,7 @@
       <c r="K121" s="6"/>
       <c r="L121" s="10"/>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="6"/>
       <c r="C122" s="16"/>
@@ -4074,7 +4072,7 @@
       <c r="K122" s="6"/>
       <c r="L122" s="10"/>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="6"/>
       <c r="C123" s="16"/>
@@ -4087,7 +4085,7 @@
       <c r="K123" s="6"/>
       <c r="L123" s="10"/>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="6"/>
       <c r="C124" s="16"/>
@@ -4100,7 +4098,7 @@
       <c r="K124" s="6"/>
       <c r="L124" s="10"/>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="6"/>
       <c r="C125" s="16"/>
@@ -4113,7 +4111,7 @@
       <c r="K125" s="6"/>
       <c r="L125" s="10"/>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="6"/>
       <c r="C126" s="16"/>
@@ -4126,7 +4124,7 @@
       <c r="K126" s="6"/>
       <c r="L126" s="10"/>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="6"/>
       <c r="C127" s="16"/>
@@ -4139,7 +4137,7 @@
       <c r="K127" s="6"/>
       <c r="L127" s="10"/>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="6"/>
       <c r="C128" s="16"/>
@@ -4152,7 +4150,7 @@
       <c r="K128" s="6"/>
       <c r="L128" s="10"/>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="6"/>
       <c r="C129" s="16"/>
@@ -4165,7 +4163,7 @@
       <c r="K129" s="6"/>
       <c r="L129" s="10"/>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="6"/>
       <c r="C130" s="16"/>
@@ -4178,7 +4176,7 @@
       <c r="K130" s="6"/>
       <c r="L130" s="10"/>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="6"/>
       <c r="C131" s="16"/>
@@ -4191,7 +4189,7 @@
       <c r="K131" s="6"/>
       <c r="L131" s="10"/>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="6"/>
       <c r="C132" s="16"/>
@@ -4204,7 +4202,7 @@
       <c r="K132" s="6"/>
       <c r="L132" s="10"/>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="6"/>
       <c r="C133" s="16"/>
@@ -4217,7 +4215,7 @@
       <c r="K133" s="6"/>
       <c r="L133" s="10"/>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="6"/>
       <c r="C134" s="16"/>
@@ -4230,7 +4228,7 @@
       <c r="K134" s="6"/>
       <c r="L134" s="10"/>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="6"/>
       <c r="C135" s="16"/>
@@ -4243,7 +4241,7 @@
       <c r="K135" s="6"/>
       <c r="L135" s="10"/>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="6"/>
       <c r="C136" s="16"/>
@@ -4256,7 +4254,7 @@
       <c r="K136" s="6"/>
       <c r="L136" s="10"/>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="6"/>
       <c r="C137" s="16"/>
@@ -4269,7 +4267,7 @@
       <c r="K137" s="6"/>
       <c r="L137" s="10"/>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="6"/>
       <c r="C138" s="16"/>
@@ -4282,7 +4280,7 @@
       <c r="K138" s="6"/>
       <c r="L138" s="10"/>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="6"/>
       <c r="C139" s="16"/>
@@ -4295,7 +4293,7 @@
       <c r="K139" s="6"/>
       <c r="L139" s="10"/>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="6"/>
       <c r="C140" s="16"/>
@@ -4308,7 +4306,7 @@
       <c r="K140" s="6"/>
       <c r="L140" s="10"/>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="6"/>
       <c r="C141" s="16"/>
@@ -4321,7 +4319,7 @@
       <c r="K141" s="6"/>
       <c r="L141" s="10"/>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="6"/>
       <c r="C142" s="16"/>
